--- a/2 Output/Phase1_Baseline_Executive/tables/phase1_baseline_executive_results.xlsx
+++ b/2 Output/Phase1_Baseline_Executive/tables/phase1_baseline_executive_results.xlsx
@@ -1135,10 +1135,10 @@
     <t>Appropriate response to noncompliance with mediated agreement</t>
   </si>
   <si>
-    <t>Appropriate response to non-compliance with mediated agreement</t>
-  </si>
-  <si>
-    <t>Knowledge of when ADR is not appropriate</t>
+    <t>Reported frequency of compliance with mediated agreements</t>
+  </si>
+  <si>
+    <t>Perceived prevention of escalation to police or courts</t>
   </si>
   <si>
     <t>ADR barriers</t>

--- a/2 Output/Phase1_Baseline_Executive/tables/phase1_baseline_executive_results.xlsx
+++ b/2 Output/Phase1_Baseline_Executive/tables/phase1_baseline_executive_results.xlsx
@@ -1651,7 +1651,7 @@
     <t>Women members participate actively when present, 0-1</t>
   </si>
   <si>
-    <t>Mechanism exists to consider women's perspectives where no women serve</t>
+    <t>Reported mechanism to consider women's perspectives in case handling</t>
   </si>
   <si>
     <t>Decision/agreement/referral validated by more than one member, 0-1</t>
